--- a/examples/demo_data/2026年销售台账.xlsx
+++ b/examples/demo_data/2026年销售台账.xlsx
@@ -455,7 +455,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>杭州云栖科技</t>
+          <t>示例科技A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -482,7 +482,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>深圳前海贸易</t>
+          <t>示例贸易B</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -497,7 +497,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>13900000002</t>
+          <t>13800000002</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -509,7 +509,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>北京智联信息</t>
+          <t>示例信息C</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -524,7 +524,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>13700000003</t>
+          <t>13800000003</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -536,7 +536,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>成都天府零售</t>
+          <t>示例零售D</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -551,7 +551,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>13600000004</t>
+          <t>13800000004</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>苏州工业园制造</t>
+          <t>示例制造E</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>13500000005</t>
+          <t>13800000005</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -597,7 +597,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>广州珠江商贸</t>
+          <t>示例商贸F</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>13900000006</t>
+          <t>13800000006</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>杭州云栖科技</t>
+          <t>示例科技A</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>深圳前海贸易</t>
+          <t>示例贸易B</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -722,7 +722,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>杭州云栖科技</t>
+          <t>示例科技A</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>北京智联信息</t>
+          <t>示例信息C</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -774,7 +774,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>成都天府零售</t>
+          <t>示例零售D</t>
         </is>
       </c>
       <c r="C6" t="n">
